--- a/output/pdf_financials_xlsx/MQM.xlsx
+++ b/output/pdf_financials_xlsx/MQM.xlsx
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7.596045</v>
+        <v>-7.596045</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.985443</v>
+        <v>-2.985443</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.605075</v>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>7.596045</v>
+        <v>-7.596045</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.985443</v>
+        <v>-2.985443</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.605075</v>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>7.596045</v>
+        <v>-7.596045</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.985443</v>
+        <v>-2.985443</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.605075</v>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>39.979184</v>
+        <v>-39.979184</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>49.757383</v>
+        <v>-49.757383</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>32.1015</v>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>7.596045</v>
+        <v>-7.596045</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.985443</v>
+        <v>-2.985443</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.605317</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>7.613813</v>
+        <v>-7.578277</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.999051</v>
+        <v>-2.971835</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.586435</v>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -6168,49 +6168,49 @@
         <v>5.159199</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.28893</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.074179</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>7.222679</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.518332</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.299961</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>8.360644000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.473314</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.473314</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.542566000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.574579</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.583214999999999</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.866334999999999</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>8.921232</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>9.875325</v>
       </c>
     </row>
     <row r="93">
@@ -7702,31 +7702,31 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.531768</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.648059</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.21263</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.051824</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.01417</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.013836</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.009363</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>0</v>
@@ -7735,16 +7735,16 @@
         <v>0</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06611400000000001</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0295</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.06895999999999999</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.23857</v>
       </c>
     </row>
     <row r="119">
@@ -10002,7 +10002,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10832,7 +10836,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -12064,7 +12072,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -14460,7 +14472,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -18342,7 +18358,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -24134,7 +24154,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -24234,7 +24258,11 @@
           <t>Cost recovery on exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -27194,7 +27222,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -29802,7 +29834,11 @@
           <t>Exploration and evaluation expenditure 7</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -51714,13 +51750,13 @@
         </is>
       </c>
       <c r="E414" s="5" t="n">
-        <v>7.596045</v>
+        <v>-7.596045</v>
       </c>
       <c r="F414" s="5" t="n">
-        <v>2.985443</v>
+        <v>-2.985443</v>
       </c>
       <c r="G414" s="5" t="n">
-        <v>1.605075</v>
+        <v>-1.605075</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MQM.xlsx
+++ b/output/pdf_financials_xlsx/MQM.xlsx
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.134481</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002844</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.000242</v>
@@ -1089,28 +1089,28 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.003333</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.006433</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000345</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000803</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.002229</v>
       </c>
     </row>
     <row r="13">
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.596045</v>
+        <v>-7.461564</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.985443</v>
+        <v>-2.982599</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.605317</v>
@@ -2090,28 +2090,28 @@
         <v>0.258734</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.812748</v>
+        <v>0.809415</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.305118</v>
+        <v>-0.311551</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.412013</v>
+        <v>-0.41203</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.122166</v>
+        <v>-0.122511</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.478868</v>
+        <v>-0.478876</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.064596</v>
+        <v>-0.065399</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.16764</v>
+        <v>-0.167646</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1.590049</v>
+        <v>1.58782</v>
       </c>
     </row>
     <row r="28">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.578277</v>
+        <v>-7.443796</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.971835</v>
+        <v>-2.968991</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.586435</v>
@@ -2212,28 +2212,28 @@
         <v>0.258734</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.8157219999999999</v>
+        <v>0.812389</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.29917</v>
+        <v>-0.305603</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.406065</v>
+        <v>-0.406082</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.117402</v>
+        <v>-0.117747</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.478868</v>
+        <v>-0.478876</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.064596</v>
+        <v>-0.065399</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.16764</v>
+        <v>-0.167646</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1.590049</v>
+        <v>1.58782</v>
       </c>
     </row>
     <row r="30">
@@ -2541,22 +2541,22 @@
         <v>0.931481</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.6412949999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.7852749999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.426699</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.275998</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.073808</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>1.507368</v>
       </c>
     </row>
     <row r="35">
@@ -2663,22 +2663,22 @@
         <v>1.140665</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.178245</v>
+        <v>0.81954</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.232075</v>
+        <v>1.01735</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.084263</v>
+        <v>0.510962</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.448216</v>
+        <v>0.724214</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.628375</v>
+        <v>0.702183</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>2.813</v>
+        <v>4.320368</v>
       </c>
     </row>
     <row r="37">
@@ -3395,22 +3395,22 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.6412949999999999</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.7852749999999999</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.426699</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.31682</v>
+        <v>0.040822</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.115538</v>
+        <v>0.04173</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1.861109</v>
+        <v>0.353741</v>
       </c>
     </row>
     <row r="49">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -39510,7 +39510,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -51538,7 +51538,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E412" s="5" t="n">

--- a/output/pdf_financials_xlsx/MQM.xlsx
+++ b/output/pdf_financials_xlsx/MQM.xlsx
@@ -4378,55 +4378,55 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.054763</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.047294</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.428944</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.142054</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.119202</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.073062</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.004422</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.002797</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.00297</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.001422</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.028442</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.002785</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.005672</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>0.090892</v>
       </c>
     </row>
     <row r="65">
@@ -4628,49 +4628,49 @@
         <v>0.022329</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.071294</v>
+        <v>0.118588</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.643944</v>
+        <v>1.072888</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.152054</v>
+        <v>0.294108</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.134202</v>
+        <v>0.253404</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.081062</v>
+        <v>0.154124</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.104422</v>
+        <v>0.108844</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.168797</v>
+        <v>0.171594</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.02897</v>
+        <v>0.03194</v>
       </c>
       <c r="M68" s="3" t="n">
         <v>0.016</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.014422</v>
+        <v>0.015844</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.015678</v>
+        <v>0.016856</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.039442</v>
+        <v>0.067884</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.019785</v>
+        <v>0.02257</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0.024672</v>
+        <v>0.030344</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.132892</v>
+        <v>0.223784</v>
       </c>
     </row>
     <row r="69">
@@ -5061,10 +5061,10 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.461063</v>
+        <v>0.319009</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.012742</v>
+        <v>0.009771999999999999</v>
       </c>
       <c r="M75" s="3" t="n">
         <v>0.01103</v>
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003033</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -8748,7 +8748,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003033</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -8813,7 +8813,7 @@
         <v>-0.373036</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-0.303832</v>
+        <v>-0.306865</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.292462</v>
@@ -22052,7 +22052,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
